--- a/tips.xlsx
+++ b/tips.xlsx
@@ -1258,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1846,9 +1846,24 @@
 System.out.println(sortedByLength);</v>
       </c>
     </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>Collections.reverse(list);</v>
+      </c>
+      <c r="B40" t="str">
+        <v>倒序。</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">reverse = 翻面
+sort(reverseOrder) = 排序（降序）</v>
+      </c>
+      <c r="D40" t="str">
+        <v>List&lt;Integer&gt; list = new ArrayList&lt;&gt;(List.of(3,1,2));//// [2,1,3]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tips.xlsx
+++ b/tips.xlsx
@@ -1258,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1302,7 +1302,7 @@
         <v>List&lt;Integer&gt; list = Arrays.asList(1,2,3);</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>List.of(...)</v>
       </c>
@@ -1310,10 +1310,11 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>List&lt;Integer&gt; list = List.of(1,2,3);</v>
+        <v>List.of 不可修改</v>
+      </c>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;Integer&gt; list = List.of(1,2,3);
+list.add(4); // ❌ 报错</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -1861,9 +1862,73 @@
         <v>List&lt;Integer&gt; list = new ArrayList&lt;&gt;(List.of(3,1,2));//// [2,1,3]</v>
       </c>
     </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>String.join()</v>
+      </c>
+      <c r="B41" t="str">
+        <v>List -&gt; String</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">stream写法更灵活
+String res = list.stream()
+      .collect(Collectors.joining(","));</v>
+      </c>
+      <c r="D41" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;String&gt; list = List.of("apple", "banana", "orange");
+String res = String.join(",", list);或者用</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>list.toString();</v>
+      </c>
+      <c r="B42" t="str">
+        <v>list转String，直接 toString（简单但格式固定）</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">特殊：无分隔符拼接
+String res = String.join("", list); 输出结果：applebananaorange</v>
+      </c>
+      <c r="D42" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;Integer&gt; list = List.of(1,2,3);
+String res = list.toString();
+System.out.println(res); // [1, 2, 3]</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>不同方法list转string</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;String&gt; → String      String.join(",", list)
+List&lt;Integer&gt; → String     stream + map + joining
+需要格式控制               Collectors.joining()</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>List&lt;Integer&gt; → String</v>
+      </c>
+      <c r="B44" t="str">
+        <v>List&lt;Integer&gt; → String</v>
+      </c>
+      <c r="C44" t="str">
+        <v>需要先转 String，stream + map + joining</v>
+      </c>
+      <c r="D44" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;Integer&gt; list = List.of(1,2,3);
+String res = list.stream().map(String::valueOf)
+             .collect(Collectors.joining(","));
+System.out.println(res); // 1,2,3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tips.xlsx
+++ b/tips.xlsx
@@ -2384,7 +2384,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2988,16 +2988,34 @@
 System.out.println(sb);//hallo</v>
       </c>
     </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>a.compareTo(b)/compareToIgnoreCase（忽略大小写）</v>
+      </c>
+      <c r="B44" t="str" xml:space="preserve">
+        <v xml:space="preserve">··返回 负数 → 当前字符串小于 anotherString
+··返回 0 → 两个字符串相等
+··返回 正数 → 当前字符串大于 anotherString</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str" xml:space="preserve">
+        <v xml:space="preserve">String x = "abc";
+String y = "abd";
+System.out.println(x.compareTo(y)); // -1 → 因为 'c' &lt; 'd'</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -3278,14 +3296,32 @@
       </c>
     </row>
     <row r="21" xml:space="preserve">
-      <c r="A21" t="str" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>比较单个字符chr == 'c'</v>
+      </c>
+      <c r="B21" t="str">
+        <v>char 比较要用 ==,string比较用equals</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str" xml:space="preserve">
+        <v xml:space="preserve">if(c == 'A') {
+    countA++;
+} else if(c == 'L') {
+    countL++;
+}</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str" xml:space="preserve">
         <v xml:space="preserve">char[] arr = {'a','b'};
 System.out.println(arr);因为 println 对 char[] 做了特殊处理。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tips.xlsx
+++ b/tips.xlsx
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -826,9 +826,24 @@
 System.out.println(Arrays.equals(a, b)); // true</v>
       </c>
     </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>Set&lt;String&gt; set = Arrays.stream(words).collect(Collectors.toSet());</v>
+      </c>
+      <c r="B30" t="str">
+        <v>数组 → 流 → 去重 → Set</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str" xml:space="preserve">
+        <v xml:space="preserve">String[] words = {"apple", "banana", "apple", "orange"};
+Set&lt;String&gt; set = Arrays.stream(words).collect(Collectors.toSet());//["apple", "banana", "orange"]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1505,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2189,9 +2204,30 @@
 System.out.println(list); // [0, 0, 100, 0, 0]</v>
       </c>
     </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str" xml:space="preserve">
+        <v xml:space="preserve">int[][] ans = new int[result.size()][];  // 1️⃣ 创建二维数组
+ans = result.toArray(ans);                // 2️⃣ List → 数组</v>
+      </c>
+      <c r="B46" t="str" xml:space="preserve">
+        <v xml:space="preserve">List 转成二维数组，List&lt;int[]&gt; → int[][]
+步骤：
+1. 创建 int[][]，第一维长度 = list.size()
+2. 每行 = list.get(i)</v>
+      </c>
+      <c r="C46" t="str">
+        <v>result 是一个 List&lt;int[]&gt;（List 中每个元素是一个数组）所以 ans.length = result.size()</v>
+      </c>
+      <c r="D46" t="str" xml:space="preserve">
+        <v xml:space="preserve">List&lt;int[]&gt; result = new ArrayList&lt;&gt;();
+result.add(new int[]{1,2});
+result.add(new int[]{3,4,5});
+result.add(new int[]{6});</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tips.xlsx
+++ b/tips.xlsx
@@ -423,12 +423,15 @@
         <v>例子</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Arrays.sort(arr)</v>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Arrays.sort(arr)
+Arrays.sort(words, (a, b) -&gt; {
+            return a.charAt(a.length() - 1) - b.charAt(b.length() - 1);
+        });</v>
       </c>
       <c r="B2" t="str">
-        <v>排序</v>
+        <v>排序，或 指定的元素在数组里比较</v>
       </c>
       <c r="C2" t="str">
         <v>升序排序只好升序，降序要另外实现</v>
@@ -2420,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2654,14 +2657,14 @@
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>String.join(delimiter, list) 分隔符，要拼接的字符串集合</v>
+        <v>String.join(delimiter, list) 分隔符，要拼接的字符串集合or array</v>
       </c>
       <c r="B16" t="str" xml:space="preserve">
         <v xml:space="preserve">数组/List 拼接成 字符串
 返回string</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>String.join(分隔符, 集合/数组)</v>
       </c>
       <c r="D16" t="str">
         <v>List&lt;String&gt; list = Arrays.asList("2026", "03", "15");String result = String.join("-", list);System.out.println(result);//2026-03-15</v>
@@ -2709,7 +2712,7 @@
         <v>s.trim()</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v>toLowerCase()</v>
       </c>
@@ -2717,10 +2720,11 @@
         <v>转小写</v>
       </c>
       <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>"HELLO".toLowerCase()</v>
+        <v>返回一个新的字符串</v>
+      </c>
+      <c r="D20" t="str" xml:space="preserve">
+        <v xml:space="preserve">String str = "Hello World!";
+String lower = str.toLowerCase()</v>
       </c>
     </row>
     <row r="21">
@@ -2821,12 +2825,14 @@
         <v>String b = Integer.toString(123);</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>stringbuilder.append("hi")</v>
-      </c>
-      <c r="B28" t="str">
-        <v>拼接字符</v>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str" xml:space="preserve">
+        <v xml:space="preserve">stringbuilder.append("hi")
+sb.append(word, 0, word.length() - 1).append(" ");</v>
+      </c>
+      <c r="B28" t="str" xml:space="preserve">
+        <v xml:space="preserve">拼接字符
+或者</v>
       </c>
     </row>
     <row r="29">
@@ -3042,9 +3048,21 @@
 System.out.println(x.compareTo(y)); // -1 → 因为 'c' &lt; 'd'</v>
       </c>
     </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>sb.append(word, 0, word.length() - 1);</v>
+      </c>
+      <c r="B45" t="str" xml:space="preserve">
+        <v xml:space="preserve">等价于：
+sb.append(word.substring(0, word.length() - 1));</v>
+      </c>
+      <c r="C45" t="str">
+        <v>append(字符串, 起始下标, 结束下标)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3857,7 +3875,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4114,9 +4132,24 @@
 System.out.println(map);//{b=1, a=3, n=2}</v>
       </c>
     </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1.	map.getOrDefault(c, someDefault)
+	2.	map.putIfAbsent(c, nextLetter)</v>
+      </c>
+      <c r="B21" t="str" xml:space="preserve">
+        <v xml:space="preserve">•	如果 c 在 map 中有值，返回值
+•	如果没有，返回 someDefault</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">putIfAbsent
+•	如果 c 不存在，则放入 nextLetter
+•	如果已经存在，保持原来的映射，这样就天然忽略重复字母，只给第一次出现的字母分配映射。</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tips.xlsx
+++ b/tips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yan/develop/projects/leetcodetips/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25B3D29-BB00-0546-8B39-86116EBAAFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA6549-0540-BA4B-B657-0225C67180C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="600" windowWidth="51200" windowHeight="27040" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="600" windowWidth="51200" windowHeight="27040" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -26,15 +26,14 @@
     <sheet name="PriorityQueue" sheetId="9" r:id="rId11"/>
     <sheet name="stream" sheetId="10" r:id="rId12"/>
     <sheet name="数组集合互换" sheetId="15" r:id="rId13"/>
-    <sheet name="chronounit" sheetId="13" r:id="rId14"/>
-    <sheet name="Sheet5" sheetId="14" r:id="rId15"/>
+    <sheet name="Sheet5" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="754">
   <si>
     <t>方法</t>
   </si>
@@ -2526,9 +2525,6 @@
   </si>
   <si>
     <t>双端操作（Deque 精髓）</t>
-  </si>
-  <si>
-    <t>ChronoUnit.DAYS.between</t>
   </si>
   <si>
     <t>import java.util.*;</t>
@@ -4406,19 +4402,19 @@
   <sheetData>
     <row r="1" spans="1:4" ht="133" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="C1" s="5" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -4432,136 +4428,136 @@
     </row>
     <row r="3" spans="1:4" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="104" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="70" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="53" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="36" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="87" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.25">
@@ -4588,11 +4584,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2055062-C711-1242-B95F-E7027316E8D8}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E84612F-84E3-D249-9027-B5240467B151}">
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -4600,144 +4596,129 @@
         <v>692</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E84612F-84E3-D249-9027-B5240467B151}">
-  <dimension ref="A1:A34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>693</v>
-      </c>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
